--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20241.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -82,16 +82,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>MONTERD</t>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>GARIBAY</t>
   </si>
   <si>
     <t>MOLINA</t>
@@ -100,85 +94,43 @@
     <t>PLIEGO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>MACUISTLE</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
     <t>LORENZO</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>INGRID ABIGAIL</t>
-  </si>
-  <si>
-    <t>ISAI</t>
+    <t>ESTRELLA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>LIZBETH MARIAM</t>
   </si>
   <si>
     <t>ANGEL FRANCISCO</t>
   </si>
   <si>
+    <t>MYA YAMILET</t>
+  </si>
+  <si>
+    <t>VALERIA JUNUET</t>
+  </si>
+  <si>
     <t>CALEB SANTIAGO</t>
-  </si>
-  <si>
-    <t>MYA YAMILET</t>
-  </si>
-  <si>
-    <t>MARIA KAREN</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>NAARA SAFIR</t>
-  </si>
-  <si>
-    <t>MAXIMILIANO</t>
-  </si>
-  <si>
-    <t>LUZ ELENA</t>
   </si>
 </sst>
 </file>
@@ -774,16 +726,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>97.5</v>
+      </c>
+      <c r="H2">
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -797,16 +752,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>87.8</v>
+      </c>
+      <c r="H3">
+        <v>5.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -820,16 +778,19 @@
         <v>48</v>
       </c>
       <c r="D4">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H4">
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -843,16 +804,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>94.44</v>
+      </c>
+      <c r="H5">
+        <v>6.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -866,16 +830,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>94.59</v>
+      </c>
+      <c r="H6">
+        <v>6.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -889,16 +856,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>93.94</v>
+      </c>
+      <c r="H7">
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -954,16 +924,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>85</v>
+        <v>97.5</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -980,16 +950,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>78.05</v>
+        <v>87.8</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1006,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>72.92</v>
+        <v>83.33</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1032,16 +1002,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>83.33</v>
+        <v>94.44</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1058,16 +1028,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>86.48999999999999</v>
+        <v>94.59</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1084,16 +1054,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>81.81999999999999</v>
+        <v>93.94</v>
       </c>
       <c r="H7">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -1103,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1135,22 +1105,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920314</v>
+        <v>24330051920250</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
         <v>32</v>
       </c>
-      <c r="D2" t="s">
-        <v>42</v>
-      </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1158,16 +1128,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920129</v>
+        <v>24330051920345</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
         <v>33</v>
-      </c>
-      <c r="D3" t="s">
-        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1181,16 +1151,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920352</v>
+        <v>24330051920347</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
         <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1204,16 +1174,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920281</v>
+        <v>24330051920117</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
         <v>35</v>
-      </c>
-      <c r="D5" t="s">
-        <v>45</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1227,16 +1197,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920347</v>
+        <v>24330051920349</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
         <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>46</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1253,13 +1223,13 @@
         <v>24330051920351</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
         <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>47</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1268,144 +1238,6 @@
         <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>24330051920117</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>24330051920086</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>24330051920115</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920162</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920057</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920167</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20241.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="32">
   <si>
     <t>Mat</t>
   </si>
@@ -82,30 +82,18 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
     <t>GARIBAY</t>
   </si>
   <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
     <t>PLIEGO</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>MARIN</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>MACUISTLE</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
@@ -115,13 +103,7 @@
     <t>LORENZO</t>
   </si>
   <si>
-    <t>ESTRELLA MONTSERRAT</t>
-  </si>
-  <si>
     <t>LIZBETH MARIAM</t>
-  </si>
-  <si>
-    <t>ANGEL FRANCISCO</t>
   </si>
   <si>
     <t>MYA YAMILET</t>
@@ -1073,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1105,16 +1087,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920250</v>
+        <v>24330051920345</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1128,16 +1110,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920345</v>
+        <v>24330051920117</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1151,16 +1133,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920347</v>
+        <v>24330051920349</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1174,16 +1156,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920117</v>
+        <v>24330051920351</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1192,52 +1174,6 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>24330051920349</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>24330051920351</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20241.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="35">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CORTES</t>
+  </si>
+  <si>
     <t>GARIBAY</t>
   </si>
   <si>
@@ -91,6 +94,9 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
@@ -101,6 +107,9 @@
   </si>
   <si>
     <t>LORENZO</t>
+  </si>
+  <si>
+    <t>VERONICA ITZEL</t>
   </si>
   <si>
     <t>LIZBETH MARIAM</t>
@@ -1055,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1087,22 +1096,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920345</v>
+        <v>24330051920336</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1110,16 +1119,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920117</v>
+        <v>24330051920345</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1133,16 +1142,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920349</v>
+        <v>24330051920117</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1156,16 +1165,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920351</v>
+        <v>24330051920349</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1174,6 +1183,29 @@
         <v>11</v>
       </c>
       <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>24330051920351</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20241.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,15 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
@@ -94,6 +103,15 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>OROZCO</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MACUISTLE</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -107,6 +125,15 @@
   </si>
   <si>
     <t>LORENZO</t>
+  </si>
+  <si>
+    <t>ANGEL ALEXANDER</t>
+  </si>
+  <si>
+    <t>ESTRELLA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>ANGEL FRANCISCO</t>
   </si>
   <si>
     <t>VERONICA ITZEL</t>
@@ -1064,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1096,39 +1123,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920336</v>
+        <v>24330051920328</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920345</v>
+        <v>24330051920250</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1137,21 +1164,21 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920117</v>
+        <v>24330051920347</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1160,27 +1187,27 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920349</v>
+        <v>24330051920336</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1188,16 +1215,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920351</v>
+        <v>24330051920345</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1206,6 +1233,75 @@
         <v>11</v>
       </c>
       <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>24330051920117</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>24330051920349</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>24330051920351</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20241.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="53">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,15 @@
     <t>CID</t>
   </si>
   <si>
+    <t>PARADA</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
@@ -106,6 +115,15 @@
     <t>OROZCO</t>
   </si>
   <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
     <t>MARIN</t>
   </si>
   <si>
@@ -128,6 +146,15 @@
   </si>
   <si>
     <t>ANGEL ALEXANDER</t>
+  </si>
+  <si>
+    <t>MARCO DIDIEL</t>
+  </si>
+  <si>
+    <t>NAARA SAFIR</t>
+  </si>
+  <si>
+    <t>YOSHUA RAFAEL</t>
   </si>
   <si>
     <t>ESTRELLA MONTSERRAT</t>
@@ -1091,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1129,10 +1156,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1146,85 +1173,85 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920250</v>
+        <v>24330051920404</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920347</v>
+        <v>24330051920162</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920336</v>
+        <v>24330051920259</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920345</v>
+        <v>24330051920250</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1233,21 +1260,21 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920117</v>
+        <v>24330051920347</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1256,27 +1283,27 @@
         <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920349</v>
+        <v>24330051920336</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1284,16 +1311,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920351</v>
+        <v>24330051920345</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1302,6 +1329,75 @@
         <v>11</v>
       </c>
       <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>24330051920117</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920349</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920351</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20241.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -82,100 +82,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>PARADA</t>
-  </si>
-  <si>
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>GARIBAY</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>OROZCO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>SOLIS</t>
   </si>
   <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MACUISTLE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>ANGEL ALEXANDER</t>
-  </si>
-  <si>
-    <t>MARCO DIDIEL</t>
+    <t>MARIA</t>
   </si>
   <si>
     <t>NAARA SAFIR</t>
   </si>
   <si>
-    <t>YOSHUA RAFAEL</t>
-  </si>
-  <si>
-    <t>ESTRELLA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>ANGEL FRANCISCO</t>
-  </si>
-  <si>
-    <t>VERONICA ITZEL</t>
-  </si>
-  <si>
-    <t>LIZBETH MARIAM</t>
-  </si>
-  <si>
-    <t>MYA YAMILET</t>
-  </si>
-  <si>
-    <t>VALERIA JUNUET</t>
-  </si>
-  <si>
-    <t>CALEB SANTIAGO</t>
+    <t>ISAI</t>
   </si>
 </sst>
 </file>
@@ -969,16 +891,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G2">
-        <v>97.5</v>
+        <v>95</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -995,13 +917,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>87.8</v>
+        <v>97.56</v>
       </c>
       <c r="H3">
         <v>6.8</v>
@@ -1021,16 +943,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G4">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1099,16 +1021,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>93.94</v>
+        <v>96.97</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1118,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1150,22 +1072,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920328</v>
+        <v>24330051920162</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1173,231 +1095,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920404</v>
+        <v>24330051920019</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>24330051920162</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>24330051920259</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>24330051920250</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>24330051920347</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>24330051920336</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>24330051920345</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>24330051920117</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920349</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920351</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Sánchez Rene Aurelio - Estadisticos 20241.xlsx
+++ b/docentes/González Sánchez Rene Aurelio - Estadisticos 20241.xlsx
@@ -82,19 +82,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>SOLIS</t>
+    <t>RANGEL</t>
   </si>
   <si>
     <t>MARIA</t>
   </si>
   <si>
-    <t>NAARA SAFIR</t>
+    <t>AXEL BENITO</t>
   </si>
   <si>
     <t>ISAI</t>
@@ -969,16 +969,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>94.44</v>
+        <v>97.22</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -995,16 +995,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G6">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1072,7 +1072,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920162</v>
+        <v>24330051920329</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -1087,10 +1087,10 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
